--- a/data/EVALUACIONES/MOVILIDAD/MOVILIDAD.xlsx
+++ b/data/EVALUACIONES/MOVILIDAD/MOVILIDAD.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30501"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\EVALUACIONES\MOVILIDAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{112044BE-9BEC-4AA1-B456-77D479CBE3AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1DFFC70-40D4-4F75-A416-4F8AB0C9B457}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{112044BE-9BEC-4AA1-B456-77D479CBE3AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0902250F-E81C-472E-A97E-1A1272D4CD57}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>Fecha</t>
   </si>
@@ -67,9 +67,6 @@
   </si>
   <si>
     <t>Ikki_Muller_Salak</t>
-  </si>
-  <si>
-    <t>Alejandro_Garcia_Gumiel</t>
   </si>
   <si>
     <t>Rodri_Sanchez_Ramos</t>
@@ -211,8 +208,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{47DCDBC4-934F-4BB8-8403-1163E6A946CF}" name="Tabla1" displayName="Tabla1" ref="A1:H27" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="A1:H27" xr:uid="{F24D9BFF-4F02-4AC6-9C99-CC9D7330899E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{47DCDBC4-934F-4BB8-8403-1163E6A946CF}" name="Tabla1" displayName="Tabla1" ref="A1:H26" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:H26" xr:uid="{F24D9BFF-4F02-4AC6-9C99-CC9D7330899E}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{B90CC2EA-DED7-4B50-9C01-6648707B7686}" name="Fecha" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{49BFBD1B-88C4-49EF-ACC0-907CF6D29923}" name="Nombre"/>
@@ -524,7 +521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FF0B100-72AE-4E6A-8897-D79B621AF892}">
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="28.5546875" bestFit="1" customWidth="1"/>
@@ -726,22 +723,22 @@
         <v>14</v>
       </c>
       <c r="C8">
-        <v>10.3</v>
+        <v>11.8</v>
       </c>
       <c r="D8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E8">
-        <v>42.1</v>
+        <v>40.5</v>
       </c>
       <c r="F8">
-        <v>33.299999999999997</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="G8">
-        <v>68.2</v>
+        <v>73.599999999999994</v>
       </c>
       <c r="H8">
-        <v>70.5</v>
+        <v>75.900000000000006</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -752,22 +749,22 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <v>11.8</v>
+        <v>10.8</v>
       </c>
       <c r="D9">
         <v>10</v>
       </c>
       <c r="E9">
-        <v>40.5</v>
+        <v>37</v>
       </c>
       <c r="F9">
-        <v>36.200000000000003</v>
+        <v>30.2</v>
       </c>
       <c r="G9">
-        <v>73.599999999999994</v>
+        <v>71.8</v>
       </c>
       <c r="H9">
-        <v>75.900000000000006</v>
+        <v>77.900000000000006</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -778,22 +775,22 @@
         <v>16</v>
       </c>
       <c r="C10">
-        <v>10.8</v>
+        <v>5.5</v>
       </c>
       <c r="D10">
-        <v>10</v>
+        <v>11.3</v>
       </c>
       <c r="E10">
-        <v>37</v>
+        <v>42.1</v>
       </c>
       <c r="F10">
-        <v>30.2</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="G10">
-        <v>71.8</v>
+        <v>72.900000000000006</v>
       </c>
       <c r="H10">
-        <v>77.900000000000006</v>
+        <v>80.3</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -804,22 +801,22 @@
         <v>17</v>
       </c>
       <c r="C11">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="D11">
-        <v>11.3</v>
+        <v>6.5</v>
       </c>
       <c r="E11">
-        <v>42.1</v>
+        <v>30.7</v>
       </c>
       <c r="F11">
-        <v>33.299999999999997</v>
+        <v>31</v>
       </c>
       <c r="G11">
-        <v>72.900000000000006</v>
+        <v>71.099999999999994</v>
       </c>
       <c r="H11">
-        <v>80.3</v>
+        <v>71.099999999999994</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
@@ -830,22 +827,22 @@
         <v>18</v>
       </c>
       <c r="C12">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="D12">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="E12">
-        <v>30.7</v>
+        <v>30</v>
       </c>
       <c r="F12">
-        <v>31</v>
+        <v>30.8</v>
       </c>
       <c r="G12">
-        <v>71.099999999999994</v>
+        <v>78.400000000000006</v>
       </c>
       <c r="H12">
-        <v>71.099999999999994</v>
+        <v>80.900000000000006</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
@@ -856,22 +853,22 @@
         <v>19</v>
       </c>
       <c r="C13">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="D13">
-        <v>7</v>
+        <v>3.9</v>
       </c>
       <c r="E13">
-        <v>30</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="F13">
-        <v>30.8</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="G13">
-        <v>78.400000000000006</v>
+        <v>69.3</v>
       </c>
       <c r="H13">
-        <v>80.900000000000006</v>
+        <v>65.3</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
@@ -882,22 +879,22 @@
         <v>20</v>
       </c>
       <c r="C14">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D14">
-        <v>3.9</v>
+        <v>9.5</v>
       </c>
       <c r="E14">
-        <v>20.399999999999999</v>
+        <v>44.6</v>
       </c>
       <c r="F14">
-        <v>17.399999999999999</v>
+        <v>44.4</v>
       </c>
       <c r="G14">
-        <v>69.3</v>
+        <v>86.4</v>
       </c>
       <c r="H14">
-        <v>65.3</v>
+        <v>81.7</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
@@ -908,22 +905,22 @@
         <v>21</v>
       </c>
       <c r="C15">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D15">
-        <v>9.5</v>
+        <v>12</v>
       </c>
       <c r="E15">
-        <v>44.6</v>
+        <v>29.3</v>
       </c>
       <c r="F15">
-        <v>44.4</v>
+        <v>29.8</v>
       </c>
       <c r="G15">
-        <v>86.4</v>
+        <v>69.7</v>
       </c>
       <c r="H15">
-        <v>81.7</v>
+        <v>69.400000000000006</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
@@ -934,22 +931,22 @@
         <v>22</v>
       </c>
       <c r="C16">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D16">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="E16">
-        <v>29.3</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="F16">
-        <v>29.8</v>
+        <v>36.6</v>
       </c>
       <c r="G16">
-        <v>69.7</v>
+        <v>67.3</v>
       </c>
       <c r="H16">
-        <v>69.400000000000006</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
@@ -960,22 +957,22 @@
         <v>23</v>
       </c>
       <c r="C17">
-        <v>10</v>
+        <v>17.5</v>
       </c>
       <c r="D17">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="E17">
-        <v>32.799999999999997</v>
+        <v>50.2</v>
       </c>
       <c r="F17">
-        <v>36.6</v>
+        <v>47.8</v>
       </c>
       <c r="G17">
-        <v>67.3</v>
+        <v>82.6</v>
       </c>
       <c r="H17">
-        <v>67</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
@@ -986,22 +983,22 @@
         <v>24</v>
       </c>
       <c r="C18">
-        <v>17.5</v>
+        <v>6.5</v>
       </c>
       <c r="D18">
-        <v>17.5</v>
+        <v>6</v>
       </c>
       <c r="E18">
-        <v>50.2</v>
+        <v>26</v>
       </c>
       <c r="F18">
-        <v>47.8</v>
+        <v>26.1</v>
       </c>
       <c r="G18">
-        <v>82.6</v>
+        <v>70</v>
       </c>
       <c r="H18">
-        <v>89.7</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
@@ -1012,22 +1009,22 @@
         <v>25</v>
       </c>
       <c r="C19">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="D19">
-        <v>6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="E19">
-        <v>26</v>
+        <v>28.9</v>
       </c>
       <c r="F19">
-        <v>26.1</v>
+        <v>26.3</v>
       </c>
       <c r="G19">
-        <v>70</v>
+        <v>76.7</v>
       </c>
       <c r="H19">
-        <v>71</v>
+        <v>72.099999999999994</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
@@ -1038,22 +1035,22 @@
         <v>26</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D20">
-        <v>4.5999999999999996</v>
+        <v>11.5</v>
       </c>
       <c r="E20">
-        <v>28.9</v>
+        <v>35.9</v>
       </c>
       <c r="F20">
-        <v>26.3</v>
+        <v>32.6</v>
       </c>
       <c r="G20">
-        <v>76.7</v>
+        <v>73</v>
       </c>
       <c r="H20">
-        <v>72.099999999999994</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
@@ -1064,22 +1061,22 @@
         <v>27</v>
       </c>
       <c r="C21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D21">
-        <v>11.5</v>
+        <v>5</v>
       </c>
       <c r="E21">
-        <v>35.9</v>
+        <v>31.2</v>
       </c>
       <c r="F21">
-        <v>32.6</v>
+        <v>35.6</v>
       </c>
       <c r="G21">
-        <v>73</v>
+        <v>77.7</v>
       </c>
       <c r="H21">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
@@ -1090,22 +1087,22 @@
         <v>28</v>
       </c>
       <c r="C22">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="D22">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="E22">
-        <v>31.2</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="F22">
-        <v>35.6</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="G22">
-        <v>77.7</v>
+        <v>80.2</v>
       </c>
       <c r="H22">
-        <v>82</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
@@ -1113,25 +1110,25 @@
         <v>46247</v>
       </c>
       <c r="B23" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C23">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="D23">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="E23">
-        <v>34.799999999999997</v>
+        <v>54</v>
       </c>
       <c r="F23">
-        <v>35.200000000000003</v>
+        <v>60.4</v>
       </c>
       <c r="G23">
-        <v>80.2</v>
+        <v>72.2</v>
       </c>
       <c r="H23">
-        <v>81.5</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
@@ -1139,81 +1136,55 @@
         <v>46247</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C24">
-        <v>4.5</v>
+        <v>11</v>
       </c>
       <c r="D24">
-        <v>3.8</v>
+        <v>9.5</v>
       </c>
       <c r="E24">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="F24">
-        <v>60.4</v>
+        <v>25</v>
       </c>
       <c r="G24">
-        <v>72.2</v>
+        <v>61.9</v>
       </c>
       <c r="H24">
-        <v>61.3</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>46247</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C25">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D25">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="E25">
-        <v>40</v>
+        <v>40.299999999999997</v>
       </c>
       <c r="F25">
-        <v>25</v>
+        <v>33.799999999999997</v>
       </c>
       <c r="G25">
-        <v>61.9</v>
+        <v>76.400000000000006</v>
       </c>
       <c r="H25">
-        <v>70.5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
-        <v>46247</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C26">
-        <v>7</v>
-      </c>
-      <c r="D26">
-        <v>8.5</v>
-      </c>
-      <c r="E26">
-        <v>40.299999999999997</v>
-      </c>
-      <c r="F26">
-        <v>33.799999999999997</v>
-      </c>
-      <c r="G26">
-        <v>76.400000000000006</v>
-      </c>
-      <c r="H26">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="1">
         <v>46247</v>
       </c>
     </row>
